--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/GPR.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/GPR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,58 +466,48 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>d_class</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 7, 9, 10, 12, 13, 14, 15, 16, 17, 21, 24, 25, 28, 34, 37, 38, 42, 44]</t>
+          <t>[4, 6, 8, 10, 14, 16, 18, 19, 21, 22, 23, 25, 26, 29, 30, 32, 33, 37, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.45138888888888895</t>
+          <t>0.7945054945054945</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.036968886184233746</t>
+          <t>0.042491303507392386</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.03736971357247025</t>
+          <t>0.08590083950602542</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.9793154071634149</t>
+          <t>0.899133347344484</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.180739164352417</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>7.0305564403533936</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 14, 15, 17, 18, 20, 23, 24, 34, 35, 37, 40, 44]</t>
+          <t>[3, 4, 7, 8, 9, 10, 12, 15, 16, 17, 21, 26, 27, 29, 30, 31, 33, 37, 38, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,753 +517,663 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5700396825396825</t>
+          <t>0.21208791208791208</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.03268354867034669</t>
+          <t>0.04485894287100018</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0489374789335836</t>
+          <t>0.0759620528332964</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.9645275959098232</t>
+          <t>0.9211237639841664</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.2297470569610596</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.292004346847534</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 9, 12, 13, 17, 26, 28, 34, 35, 37, 38, 40, 41, 44]</t>
+          <t>[5, 6, 7, 8, 12, 20, 22, 23, 24, 25, 26, 30, 34, 36, 37, 38, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5978174603174603</t>
+          <t>0.6032967032967034</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.040092610008437155</t>
+          <t>0.04101593925532106</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.04807159591442509</t>
+          <t>0.07592240023296727</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.9657717639005543</t>
+          <t>0.9212060901304742</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.2431159019470215</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>9.876509189605713</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 6, 9, 10, 11, 15, 21, 23, 26, 27, 28, 32, 34, 35, 37, 43, 44]</t>
+          <t>[3, 5, 8, 10, 11, 12, 13, 16, 18, 22, 25, 29, 30, 36, 37, 38, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6125</t>
+          <t>0.6642857142857144</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03879996569334569</t>
+          <t>0.042389505427446655</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.04492281859989645</t>
+          <t>0.08023067713492747</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.9701089319579849</t>
+          <t>0.9120099210363606</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.2435786724090576</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>10.274008512496948</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 6, 7, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 21, 23, 24, 25, 27, 28, 32, 34, 35, 37, 41, 42, 43]</t>
+          <t>[0, 1, 2, 4, 8, 10, 12, 13, 14, 15, 16, 19, 20, 22, 23, 26, 27, 29, 32, 37, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8726190476190476</t>
+          <t>0.4747252747252747</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04210433937484369</t>
+          <t>0.044285636588890794</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.046034655343725556</t>
+          <t>0.08525591445414167</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.9686110180561969</t>
+          <t>0.900642232134983</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.181796073913574</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>9.145981788635254</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 8, 9, 12, 13, 14, 15, 16, 17, 19, 21, 23, 25, 26, 27, 29, 31, 36, 37, 40, 44]</t>
+          <t>[1, 2, 6, 8, 12, 13, 14, 17, 18, 20, 21, 23, 24, 25, 26, 27, 29, 30, 31, 34, 37, 38, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5867063492063492</t>
+          <t>0.41373626373626377</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.03753701988941621</t>
+          <t>0.04407088397495494</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.042301513972365784</t>
+          <t>0.07258282556222732</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.9734955216909906</t>
+          <t>0.9279854031531057</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.2087419033050537</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>9.959457159042358</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[2, 6, 7, 8, 10, 13, 14, 16, 20, 23, 25, 26, 30, 32, 35, 37, 38, 39, 40]</t>
+          <t>[4, 6, 7, 8, 10, 13, 14, 15, 16, 17, 18, 23, 24, 27, 28, 30, 31, 32, 34, 36, 37, 38, 41, 44]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5033730158730159</t>
+          <t>0.7109890109890109</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.03493057332068796</t>
+          <t>0.043931575672389075</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.05293222369505691</t>
+          <t>0.06575879355974854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.9585000363207696</t>
+          <t>0.9408900671565574</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.2037782669067383</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>9.784252405166626</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 8, 12, 18, 21, 23, 24, 26, 27, 29, 31, 32, 33, 35, 37, 38, 41, 42, 43]</t>
+          <t>[1, 7, 8, 12, 14, 15, 17, 21, 22, 23, 26, 27, 28, 35, 37, 38, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.5236263736263737</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.043043430319861284</t>
+          <t>0.0421359169418154</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.03640563816330449</t>
+          <t>0.07008578908348029</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.9803688955013912</t>
+          <t>0.9328551470649227</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.1665995121002197</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>9.509632587432861</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1, 2, 5, 6, 7, 8, 9, 13, 14, 17, 18, 24, 25, 26, 30, 34, 35, 37, 39, 41, 42]</t>
+          <t>[1, 3, 4, 5, 8, 12, 13, 16, 17, 19, 21, 22, 23, 24, 25, 28, 37, 40, 44]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7365079365079366</t>
+          <t>0.3934065934065934</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.03696770018260627</t>
+          <t>0.0386394465496006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.04283864733418241</t>
+          <t>0.08134310645144194</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.9728181546914976</t>
+          <t>0.909552972199912</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.224294900894165</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>9.56331491470337</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 6, 8, 12, 13, 15, 20, 21, 22, 23, 24, 25, 27, 34, 35, 37, 40, 44]</t>
+          <t>[0, 2, 4, 8, 12, 13, 14, 16, 17, 18, 19, 22, 24, 25, 26, 28, 30, 35, 37, 39, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.4311507936507937</t>
+          <t>0.8093406593406594</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.03634346327920454</t>
+          <t>0.04378561588139575</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.045508010236988264</t>
+          <t>0.09495329893635562</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.9693251016346226</t>
+          <t>0.8767539786897491</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.2916259765625</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>9.825812816619873</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[2, 3, 7, 8, 9, 11, 12, 13, 14, 16, 17, 21, 26, 28, 32, 34, 36, 37, 40, 42, 43, 44]</t>
+          <t>[0, 2, 3, 4, 5, 7, 8, 11, 13, 14, 15, 17, 19, 20, 21, 22, 24, 25, 26, 28, 29, 33, 34, 36, 37, 38, 39, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9652777777777779</t>
+          <t>1.178021978021978</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.040696303265115495</t>
+          <t>0.04762478605301543</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0520727609839255</t>
+          <t>0.09540694524482496</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.9598367684698089</t>
+          <t>0.8755735318695873</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.164294719696045</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.836848974227905</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1, 4, 5, 6, 10, 12, 17, 21, 26, 31, 32, 34, 35, 37, 38, 39, 42]</t>
+          <t>[1, 5, 8, 9, 12, 13, 14, 20, 22, 25, 26, 28, 31, 32, 36, 37, 38, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.40496031746031746</t>
+          <t>0.5774725274725274</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.04117921322426668</t>
+          <t>0.04385334854537461</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.040176659522461834</t>
+          <t>0.07758770706152687</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.9760913481794495</t>
+          <t>0.917711598293153</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.2879512310028076</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.377350807189941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 5, 8, 11, 14, 16, 17, 18, 21, 37, 41, 42, 43, 44]</t>
+          <t>[1, 2, 3, 5, 8, 9, 11, 12, 13, 16, 17, 20, 21, 22, 23, 25, 28, 30, 31, 37, 38, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.584920634920635</t>
+          <t>0.6131868131868131</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.03927155558410261</t>
+          <t>0.046988837709603014</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.03946899347243324</t>
+          <t>0.0826647306779413</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.9769261778513243</t>
+          <t>0.9065900149555739</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.213505744934082</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.441306114196777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 5, 6, 8, 12, 17, 20, 21, 22, 24, 27, 31, 34, 37, 39, 42, 44]</t>
+          <t>[0, 2, 5, 8, 9, 10, 12, 13, 14, 22, 23, 24, 26, 28, 29, 31, 37, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.551984126984127</t>
+          <t>0.4032967032967033</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.037916999113147734</t>
+          <t>0.04315515557079598</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0270883317685845</t>
+          <t>0.08611499349665173</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.9891314412319054</t>
+          <t>0.8986297917947251</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.29447340965271</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.586936712265015</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[0, 3, 8, 9, 13, 16, 20, 23, 24, 28, 29, 36, 37, 39, 41, 42, 43]</t>
+          <t>[3, 4, 5, 6, 8, 9, 10, 11, 12, 13, 18, 21, 22, 23, 24, 25, 26, 29, 30, 31, 32, 33, 34, 37, 38, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.4994047619047619</t>
+          <t>0.9489010989010989</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.041248687971640954</t>
+          <t>0.045794959298106605</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.05365540861075019</t>
+          <t>0.07601301402111978</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.9573583057960133</t>
+          <t>0.9210178959917728</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.1947286128997803</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.431318283081055</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[1, 4, 5, 9, 10, 11, 12, 20, 21, 27, 29, 36, 37, 38, 41, 44]</t>
+          <t>[2, 3, 5, 7, 8, 15, 16, 18, 20, 21, 22, 24, 25, 26, 33, 34, 35, 37, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.46051587301587305</t>
+          <t>0.41373626373626377</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.038107606950122636</t>
+          <t>0.045122183051325995</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.06905200497693197</t>
+          <t>0.08781312604683347</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.9293747457030483</t>
+          <t>0.894592462430455</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.1916537284851074</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.599972724914551</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 5, 6, 8, 9, 10, 11, 12, 14, 21, 25, 26, 30, 33, 36, 37, 43]</t>
+          <t>[3, 5, 8, 9, 10, 14, 16, 18, 20, 21, 24, 25, 26, 32, 36, 37, 44]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.601388888888889</t>
+          <t>0.3423076923076923</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.0398159989165828</t>
+          <t>0.04630173599631449</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0680514461215172</t>
+          <t>0.05959124299117682</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.9314066276189135</t>
+          <t>0.9514579983309217</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.212935447692871</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.350911855697632</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 10, 12, 14, 15, 17, 18, 19, 22, 25, 27, 31, 32, 37, 38, 39, 40, 42, 43, 44]</t>
+          <t>[0, 2, 5, 8, 10, 12, 15, 17, 18, 20, 22, 24, 25, 26, 29, 37, 38, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.8347222222222221</t>
+          <t>0.4593406593406593</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.04014670381962375</t>
+          <t>0.03812701026993653</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.03993459929909013</t>
+          <t>0.09411277263507531</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.9763785746251135</t>
+          <t>0.8789262681769079</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.2572739124298096</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.4324564933776855</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 9, 11, 12, 21, 22, 23, 24, 25, 28, 34, 35, 37, 40, 44]</t>
+          <t>[3, 4, 5, 6, 8, 10, 14, 15, 16, 17, 18, 21, 23, 27, 29, 31, 32, 34, 35, 36, 37, 38, 41]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.5325396825396825</t>
+          <t>0.5087912087912088</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.038629137377172475</t>
+          <t>0.04574912155208295</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.040172645453110535</t>
+          <t>0.06082539947319353</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.9760961253905661</t>
+          <t>0.9494265324409348</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.2857117652893066</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.256282567977905</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 8, 9, 12, 14, 15, 16, 17, 19, 23, 25, 26, 27, 30, 32, 33, 35, 37, 39, 44]</t>
+          <t>[0, 2, 5, 7, 8, 10, 12, 14, 15, 16, 19, 21, 22, 24, 25, 26, 28, 31, 33, 37, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1283,1887 +1183,1662 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.6630952380952381</t>
+          <t>0.7120879120879121</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.03657687891275883</t>
+          <t>0.045370057388527424</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.05281583801018817</t>
+          <t>0.08252480390754201</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.9586823332783208</t>
+          <t>0.9069059778854123</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.309478282928467</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.618898868560791</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 5, 7, 8, 10, 11, 12, 16, 17, 23, 26, 27, 32, 34, 37, 39, 42, 44]</t>
+          <t>[3, 4, 7, 8, 11, 15, 17, 18, 21, 23, 24, 25, 28, 32, 33, 34, 35, 37, 38, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.6339285714285714</t>
+          <t>0.573076923076923</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.035794701731468426</t>
+          <t>0.043805224581622136</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.03822522617206408</t>
+          <t>0.0933665735035531</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.9783574930467343</t>
+          <t>0.8808385899142134</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.2325387001037598</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.5105061531066895</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 7, 8, 13, 14, 17, 18, 23, 24, 25, 27, 29, 30, 32, 37, 39, 42, 44]</t>
+          <t>[5, 7, 8, 9, 10, 11, 14, 16, 17, 18, 19, 21, 23, 27, 30, 31, 34, 37, 39, 41, 42]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.4801587301587301</t>
+          <t>0.6642857142857144</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.036588873757732746</t>
+          <t>0.04536996597172454</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.05119165205615559</t>
+          <t>0.07985078357560633</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.9611844513788537</t>
+          <t>0.9128412171714715</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.24130916595459</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.461623191833496</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[1, 2, 5, 6, 7, 8, 10, 13, 17, 19, 22, 26, 31, 32, 35, 37, 38, 41, 42, 44]</t>
+          <t>[2, 4, 8, 9, 12, 13, 14, 15, 21, 22, 23, 24, 26, 28, 29, 31, 37, 38, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.7658730158730159</t>
+          <t>0.5307692307692308</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.04161368296823938</t>
+          <t>0.0424075177299775</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0390283456842971</t>
+          <t>0.08448876023656884</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.9774385127838071</t>
+          <t>0.90242227978273</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.2951724529266357</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.58158802986145</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 7, 9, 10, 12, 13, 14, 19, 21, 27, 36, 37, 38, 41, 44]</t>
+          <t>[1, 2, 5, 6, 8, 10, 11, 12, 13, 14, 15, 18, 19, 20, 22, 25, 26, 28, 29, 30, 33, 35, 37, 38, 44]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.44246031746031744</t>
+          <t>0.7972527472527473</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.03635202289801839</t>
+          <t>0.041620813710206386</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.06140199545125056</t>
+          <t>0.09945962717219607</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.9441565284715113</t>
+          <t>0.8647782830160975</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.225569486618042</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.682159423828125</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 5, 6, 8, 10, 13, 19, 20, 22, 23, 24, 25, 27, 36, 37, 39, 40, 41, 42, 43, 44]</t>
+          <t>[0, 5, 11, 12, 13, 14, 17, 18, 20, 21, 23, 25, 26, 37, 38, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9253968253968254</t>
+          <t>0.4593406593406593</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.03941908102778968</t>
+          <t>0.04737063518162017</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.05136346725760397</t>
+          <t>0.10526636192817417</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.9609234598760332</t>
+          <t>0.8485281186262831</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.2176225185394287</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.593111753463745</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 6, 7, 8, 10, 14, 16, 18, 21, 23, 24, 32, 34, 35, 37, 38, 42]</t>
+          <t>[5, 7, 8, 9, 10, 11, 12, 13, 14, 15, 18, 19, 22, 24, 25, 26, 30, 31, 32, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.3813492063492064</t>
+          <t>1.121978021978022</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.035969768295113</t>
+          <t>0.046236734465705184</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.05646064532333146</t>
+          <t>0.0740411006133779</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.9527829213441554</t>
+          <t>0.9250626167219146</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.2029731273651123</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.756231307983398</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 14, 16, 19, 23, 25, 26, 28, 31, 34, 36, 37, 42, 44]</t>
+          <t>[1, 3, 5, 7, 8, 9, 10, 12, 13, 14, 15, 19, 21, 23, 25, 26, 32, 34, 37, 39, 40, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.0228174603174602</t>
+          <t>0.8994505494505494</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.035191326781462265</t>
+          <t>0.04577591037003451</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0401704700255751</t>
+          <t>0.08735913356985603</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.9760987142038474</t>
+          <t>0.8956795556343338</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.218665838241577</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.471015930175781</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[1, 3, 6, 9, 10, 11, 12, 13, 14, 15, 16, 19, 20, 23, 26, 28, 29, 30, 36, 37, 41]</t>
+          <t>[1, 2, 4, 8, 10, 12, 15, 16, 18, 19, 21, 22, 24, 27, 28, 29, 30, 32, 33, 34, 36, 37, 39, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.7880952380952381</t>
+          <t>1.0252747252747252</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.038943990331246944</t>
+          <t>0.04346271754287855</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.06398393805177137</t>
+          <t>0.07427034819975754</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.9393613713839437</t>
+          <t>0.9245978529779206</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.1426119804382324</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.863349676132202</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 5, 7, 8, 9, 10, 12, 13, 15, 18, 19, 20, 24, 25, 26, 30, 33, 35, 37, 39, 40, 44]</t>
+          <t>[1, 3, 4, 8, 10, 11, 14, 17, 18, 22, 23, 24, 25, 26, 27, 29, 30, 31, 34, 36, 37, 38, 42, 43]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.7331349206349207</t>
+          <t>0.6901098901098901</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.04121767442512968</t>
+          <t>0.04474117445255808</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0527808465977897</t>
+          <t>0.055573882766259</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.9587370624901747</t>
+          <t>0.9577823287781648</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.1639058589935303</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.783011436462402</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 6, 8, 9, 13, 15, 17, 18, 19, 23, 30, 35, 37, 38, 40, 42]</t>
+          <t>[2, 3, 4, 5, 8, 10, 12, 14, 16, 19, 20, 21, 24, 25, 27, 29, 30, 32, 33, 35, 37, 38, 39, 42, 44]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.5394841269841271</t>
+          <t>0.5159340659340659</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.0384212598298921</t>
+          <t>0.043167050866189716</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.056638789937434514</t>
+          <t>0.08073342069297972</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.9524844926549596</t>
+          <t>0.9109037346064556</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.2242040634155273</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.442274332046509</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 3, 6, 8, 9, 10, 13, 15, 16, 17, 21, 22, 27, 37, 39, 41, 43, 44]</t>
+          <t>[2, 4, 5, 6, 7, 8, 12, 14, 15, 20, 23, 24, 28, 30, 31, 34, 36, 37, 41, 42]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.6126984126984127</t>
+          <t>0.4857142857142857</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.03488917298412892</t>
+          <t>0.04603314957116705</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0418432724618591</t>
+          <t>0.06797933417514332</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.9740666439392742</t>
+          <t>0.9368306213084137</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.216136932373047</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>7.062297105789185</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 6, 8, 9, 10, 12, 13, 14, 16, 18, 23, 25, 26, 27, 31, 34, 37, 38, 39, 41, 43]</t>
+          <t>[4, 5, 6, 8, 10, 11, 12, 14, 17, 18, 19, 20, 21, 23, 24, 27, 29, 31, 32, 33, 35, 37, 38, 39, 42, 44]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.8496031746031746</t>
+          <t>0.7467032967032967</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.03698509850916586</t>
+          <t>0.04894103295312764</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.03174625984205621</t>
+          <t>0.07423952176716478</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.9850723112416727</t>
+          <t>0.9246604323755901</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.2891409397125244</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.508361339569092</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 6, 8, 9, 12, 14, 15, 16, 17, 19, 20, 22, 27, 29, 31, 36, 37, 39, 40, 41, 44]</t>
+          <t>[1, 4, 5, 7, 8, 11, 12, 13, 14, 15, 17, 19, 20, 21, 22, 24, 25, 27, 31, 34, 35, 37, 38, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.05515873015873</t>
+          <t>0.784065934065934</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.03666879028623144</t>
+          <t>0.043528873248691015</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.04482975574980046</t>
+          <t>0.08041469003828304</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.9702326493343012</t>
+          <t>0.9116058392499894</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.2759957313537598</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.672521352767944</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 6, 8, 12, 14, 15, 19, 23, 25, 27, 30, 31, 33, 37, 39, 43]</t>
+          <t>[1, 2, 3, 4, 6, 8, 10, 13, 20, 21, 22, 23, 25, 26, 27, 28, 32, 36, 37, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.5390873015873016</t>
+          <t>0.8796703296703297</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.03543300884811457</t>
+          <t>0.04400387355668182</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.04932194106030133</t>
+          <t>0.07683166031454312</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.9639680506789784</t>
+          <t>0.9193074892370281</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.2366185188293457</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.858647108078003</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[0, 11, 14, 15, 17, 18, 19, 22, 24, 25, 26, 28, 29, 30, 35, 37, 43]</t>
+          <t>[8, 11, 12, 14, 16, 19, 23, 24, 28, 32, 33, 34, 37, 38, 44]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.7289682539682539</t>
+          <t>0.44780219780219777</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.04032497925318228</t>
+          <t>0.04342054277105664</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.06707595706368533</t>
+          <t>0.08762365196351575</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.9333590477243923</t>
+          <t>0.8950468466597697</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.210430145263672</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>7.719819784164429</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 18, 19, 21, 23, 29, 36, 37, 39]</t>
+          <t>[2, 3, 4, 5, 8, 9, 10, 11, 12, 13, 14, 15, 20, 21, 22, 25, 26, 28, 30, 31, 32, 33, 36, 37, 39, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.6755952380952381</t>
+          <t>1.1631868131868133</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.03877553727680884</t>
+          <t>0.044831323686581395</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.05909081492854074</t>
+          <t>0.07454545001203951</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.9482813241542541</t>
+          <t>0.9240382303303668</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.288259267807007</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.516849756240845</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 16, 18, 19, 21, 23, 26, 27, 29, 31, 34, 37, 43]</t>
+          <t>[0, 1, 2, 5, 6, 8, 9, 10, 11, 13, 18, 20, 21, 22, 23, 24, 26, 27, 29, 34, 35, 37, 38, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.5825396825396826</t>
+          <t>0.6928571428571428</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.041443143156573395</t>
+          <t>0.04836230095784922</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.029813636385808084</t>
+          <t>0.0894709871754672</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.9868345005566634</t>
+          <t>0.8905748248242545</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.2451465129852295</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.250039100646973</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 5, 6, 7, 9, 11, 14, 17, 20, 22, 25, 27, 32, 34, 36, 37, 38, 41, 42, 44]</t>
+          <t>[1, 2, 3, 4, 5, 8, 10, 12, 14, 15, 20, 23, 24, 25, 26, 27, 32, 36, 37, 39, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.861904761904762</t>
+          <t>0.8895604395604395</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.03971106314585516</t>
+          <t>0.04184813229350644</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.06138828367753996</t>
+          <t>0.07104739363746762</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.9441814666691354</t>
+          <t>0.9309999995917366</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.280456066131592</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.592036485671997</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 5, 6, 8, 9, 10, 12, 13, 14, 18, 19, 25, 27, 29, 30, 35, 37, 39, 41, 42, 43, 44]</t>
+          <t>[1, 5, 6, 8, 9, 12, 14, 15, 16, 17, 18, 22, 23, 27, 28, 29, 30, 33, 34, 37, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.6567460317460317</t>
+          <t>0.5906593406593407</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.0371872397149523</t>
+          <t>0.042778811725509805</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0485208657325213</t>
+          <t>0.09809638813177132</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.9651289904707715</t>
+          <t>0.8684597004533312</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.2737207412719727</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.187219142913818</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 6, 7, 8, 9, 13, 14, 15, 17, 22, 23, 25, 34, 37, 41, 42, 44]</t>
+          <t>[1, 2, 3, 4, 7, 8, 10, 12, 16, 18, 20, 21, 25, 27, 28, 29, 30, 34, 36, 37, 38, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.6234126984126984</t>
+          <t>0.843956043956044</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.03436214189869414</t>
+          <t>0.04179019610930919</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.04440525059004826</t>
+          <t>0.07567227706421509</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.9707937304739345</t>
+          <t>0.9217244014184119</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.2367141246795654</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.156052350997925</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[6, 9, 13, 16, 18, 19, 20, 23, 24, 25, 26, 27, 29, 30, 35, 37, 39, 41, 44]</t>
+          <t>[1, 4, 5, 8, 12, 13, 17, 19, 20, 21, 23, 25, 32, 34, 36, 37, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.4125</t>
+          <t>0.6285714285714286</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.039965263157569</t>
+          <t>0.04798193270420135</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.044287194789500814</t>
+          <t>0.08063753376832496</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.970948819617592</t>
+          <t>0.9111152478425426</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.3480420112609863</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.141552209854126</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 15, 18, 19, 23, 25, 26, 27, 34, 36, 37, 39, 40, 42]</t>
+          <t>[0, 1, 2, 3, 4, 5, 6, 8, 11, 12, 13, 16, 17, 18, 19, 23, 26, 28, 29, 32, 33, 37, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.9255952380952381</t>
+          <t>0.9593406593406593</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.03809215605605</t>
+          <t>0.04357864015626487</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.05369390533482746</t>
+          <t>0.09939195414009908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.9572970946534899</t>
+          <t>0.8649622320353664</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.201702356338501</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.314064025878906</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 8, 9, 10, 11, 12, 14, 15, 16, 17, 18, 20, 21, 23, 26, 27, 28, 32, 34, 36, 37, 44]</t>
+          <t>[2, 5, 7, 8, 9, 10, 12, 13, 14, 16, 19, 20, 21, 23, 25, 27, 28, 30, 31, 35, 37, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.8849206349206349</t>
+          <t>0.784065934065934</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.04044040587806973</t>
+          <t>0.0467392501709538</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.04855298927156254</t>
+          <t>0.0694620912533469</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.965082802051409</t>
+          <t>0.9340448821513386</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.2653443813323975</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.060316562652588</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 7, 8, 9, 11, 12, 15, 16, 17, 18, 23, 25, 26, 30, 32, 35, 37]</t>
+          <t>[4, 8, 9, 10, 11, 13, 19, 21, 22, 25, 27, 29, 30, 34, 35, 37, 38, 39, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.5445054945054946</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.03549879688336369</t>
+          <t>0.04583312638334981</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.05139996405784882</t>
+          <t>0.08352313162347333</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.9608679077319044</t>
+          <t>0.9046399805180554</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.300987720489502</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.077142715454102</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 6, 9, 11, 13, 14, 15, 22, 23, 25, 26, 28, 29, 36, 37, 41]</t>
+          <t>[0, 4, 5, 6, 10, 14, 15, 20, 22, 23, 24, 25, 29, 34, 37, 38, 39, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.8011904761904762</t>
+          <t>0.5005494505494505</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.03888042311832961</t>
+          <t>0.04206742265420192</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.058716948521372256</t>
+          <t>0.0930024594293486</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.9489336998812071</t>
+          <t>0.8817661968988041</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.2475533485412598</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.314658880233765</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 5, 7, 8, 9, 13, 14, 16, 20, 23, 27, 29, 35, 37, 39, 42, 43, 44]</t>
+          <t>[1, 2, 3, 4, 5, 6, 9, 10, 11, 19, 20, 23, 24, 25, 26, 30, 31, 32, 33, 37, 38, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.640079365079365</t>
+          <t>0.5857142857142856</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.0387228673294998</t>
+          <t>0.04773370977496867</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.046885498757461674</t>
+          <t>0.09184882537806537</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.967439990806967</t>
+          <t>0.8846812289359618</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.094848871231079</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.126251935958862</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 10, 13, 14, 15, 21, 23, 24, 27, 28, 29, 30, 35, 37, 41, 43]</t>
+          <t>[3, 7, 8, 11, 12, 16, 17, 19, 20, 23, 28, 29, 30, 31, 32, 36, 37, 38, 39, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.49444444444444446</t>
+          <t>0.7060439560439561</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.04060180042924435</t>
+          <t>0.045580651109961956</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.04676179456441059</t>
+          <t>0.06585112366926914</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.96761157887658</t>
+          <t>0.9407239613711844</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.2310709953308105</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.126017093658447</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 7, 8, 9, 12, 13, 14, 15, 16, 17, 23, 26, 29, 31, 36, 37, 38, 39, 43]</t>
+          <t>[4, 6, 8, 9, 10, 14, 15, 16, 19, 21, 23, 24, 27, 28, 35, 37, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.4736111111111111</t>
+          <t>0.6060439560439561</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.040088739715111836</t>
+          <t>0.043574531904077694</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.043022985592108494</t>
+          <t>0.08621513600717148</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.9725837199016953</t>
+          <t>0.8983938893284195</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.2768945693969727</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.670961141586304</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 6, 7, 8, 9, 12, 13, 14, 19, 21, 24, 30, 31, 36, 37, 39, 40, 42, 44]</t>
+          <t>[1, 3, 6, 8, 10, 12, 13, 15, 16, 19, 20, 28, 31, 34, 36, 37, 38, 41]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.6075396825396826</t>
+          <t>0.5318681318681319</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.03556930399201601</t>
+          <t>0.04336519155154035</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.044192404257890394</t>
+          <t>0.05163395400246235</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.9710730464876303</t>
+          <t>0.9635562079964199</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.2908551692962646</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.3292622566223145</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[1, 4, 6, 7, 8, 10, 11, 12, 14, 21, 25, 27, 29, 32, 33, 37, 41, 42]</t>
+          <t>[2, 4, 5, 6, 7, 8, 9, 11, 13, 14, 17, 20, 21, 22, 23, 28, 31, 34, 35, 37, 39, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.670436507936508</t>
+          <t>0.8565934065934067</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.036461101034628365</t>
+          <t>0.0469322647935109</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.04902362756990212</t>
+          <t>0.08317095675794046</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.9644025960495803</t>
+          <t>0.9054424552161121</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.2015607357025146</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.968505620956421</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 6, 7, 9, 10, 11, 12, 14, 15, 25, 26, 28, 30, 32, 35, 37, 39, 40, 41, 42, 43]</t>
+          <t>[2, 3, 8, 9, 10, 12, 16, 20, 21, 25, 28, 29, 30, 32, 33, 34, 37, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.0148809523809523</t>
+          <t>0.3708791208791209</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.039987352463244634</t>
+          <t>0.04354254385886845</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.050235594523227824</t>
+          <t>0.08700961058941072</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.9626207544924064</t>
+          <t>0.8965126556966422</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.2789504528045654</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.141516923904419</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 14, 16, 17, 19, 20, 27, 29, 30, 32, 35, 37, 42, 43]</t>
+          <t>[2, 3, 4, 6, 7, 13, 14, 18, 21, 23, 25, 27, 30, 31, 34, 36, 37, 39, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.8601190476190477</t>
+          <t>0.4703296703296703</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.04113450083157655</t>
+          <t>0.04446765398272556</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0524771724947839</t>
+          <t>0.06607207797575768</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.9592105084208824</t>
+          <t>0.9403255089726484</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2.2964580059051514</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.044001340866089</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[2, 3, 9, 12, 14, 15, 16, 18, 19, 20, 21, 23, 25, 27, 34, 35, 37, 39, 40, 42]</t>
+          <t>[0, 1, 2, 4, 6, 8, 10, 12, 14, 16, 17, 18, 19, 20, 25, 28, 32, 37, 38, 41, 42]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.42142857142857143</t>
+          <t>0.6846153846153846</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.038752729613752215</t>
+          <t>0.0411834004027032</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.05921819570664968</t>
+          <t>0.08717453685142965</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.9480581061821808</t>
+          <t>0.8961199644366493</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.2303659915924072</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.988198280334473</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[2, 3, 6, 7, 8, 11, 15, 18, 19, 22, 23, 24, 25, 27, 33, 34, 37, 44]</t>
+          <t>[1, 2, 5, 8, 10, 11, 12, 14, 17, 19, 21, 22, 23, 26, 31, 32, 33, 34, 37, 38, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.6047619047619048</t>
+          <t>0.671978021978022</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.03951265973202202</t>
+          <t>0.039345370744580235</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.060433754460221686</t>
+          <t>0.09254406258032186</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9459038210963955</t>
+          <t>0.8829288421819533</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.296078681945801</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.045063018798828</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 5, 7, 9, 10, 11, 12, 14, 16, 17, 25, 26, 27, 31, 35, 37, 40, 43, 44]</t>
+          <t>[0, 1, 2, 3, 4, 6, 7, 8, 12, 13, 15, 17, 19, 20, 21, 26, 27, 33, 35, 37, 38, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.526984126984127</t>
+          <t>0.7313186813186814</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.04074485641645578</t>
+          <t>0.04621021846937663</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.04201222293953919</t>
+          <t>0.08857618019488453</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9738567990525453</t>
+          <t>0.8927526209676716</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2.3475942611694336</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.187750816345215</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 5, 8, 10, 13, 14, 17, 20, 25, 26, 27, 28, 29, 32, 34, 35, 37, 39, 40, 41, 42, 44]</t>
+          <t>[2, 3, 4, 5, 7, 8, 9, 12, 13, 14, 15, 16, 18, 20, 21, 24, 27, 28, 31, 37, 38, 42]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.0482142857142858</t>
+          <t>0.42417582417582417</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.04150643835102511</t>
+          <t>0.04269283794281971</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.04022161737183527</t>
+          <t>0.08713959849506953</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9760378104797737</t>
+          <t>0.89620321513177</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.337935447692871</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.128839492797852</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 5, 6, 7, 10, 11, 13, 14, 17, 18, 19, 24, 25, 27, 32, 34, 37, 41, 42, 43, 44]</t>
+          <t>[3, 4, 8, 11, 16, 17, 18, 20, 21, 24, 28, 29, 30, 31, 32, 33, 36, 37, 38, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.7039682539682539</t>
+          <t>0.7543956043956044</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.039954838980927505</t>
+          <t>0.04785668249033308</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.05103267060458622</t>
+          <t>0.08625303723607722</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.9614251691412818</t>
+          <t>0.8983045351126805</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2.2191853523254395</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.97756552696228</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 5, 6, 7, 8, 13, 14, 15, 16, 17, 18, 19, 22, 23, 26, 27, 29, 30, 32, 37, 40, 41, 44]</t>
+          <t>[2, 5, 6, 8, 12, 13, 15, 17, 22, 24, 26, 30, 31, 33, 38, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.8355158730158729</t>
+          <t>0.378021978021978</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.04016369927340389</t>
+          <t>0.04404756911558681</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.04604884687530401</t>
+          <t>0.09542014599421185</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9685916619260013</t>
+          <t>0.8755390975576933</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.2437171936035156</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.047380447387695</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 5, 6, 8, 9, 11, 12, 16, 18, 19, 20, 21, 22, 24, 26, 28, 32, 34, 36, 37, 39, 41, 42, 43, 44]</t>
+          <t>[2, 3, 4, 5, 8, 10, 12, 13, 14, 17, 21, 22, 24, 25, 27, 28, 37, 42, 43]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.454563492063492</t>
+          <t>0.567032967032967</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.0403195820806897</t>
+          <t>0.03705084475571575</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.04489906197351758</t>
+          <t>0.08320040603815769</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.9701405383082965</t>
+          <t>0.9053754812449546</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2.211930274963379</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.125695466995239</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[0, 2, 6, 7, 8, 13, 14, 15, 17, 19, 21, 23, 24, 28, 32, 37, 39, 40, 41, 43]</t>
+          <t>[2, 4, 8, 9, 10, 12, 14, 15, 17, 19, 22, 23, 25, 26, 27, 28, 35, 37, 38, 39, 41, 43]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.7494047619047619</t>
+          <t>0.8148351648351648</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.03818900274607032</t>
+          <t>0.04290931469312283</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.054993492452222265</t>
+          <t>0.09027736471667885</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.9552049484687004</t>
+          <t>0.8885934979382502</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.172452449798584</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.201878070831299</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 6, 7, 8, 9, 10, 12, 13, 23, 24, 26, 27, 28, 30, 34, 35, 37, 40, 42]</t>
+          <t>[1, 2, 3, 5, 8, 10, 11, 16, 20, 21, 22, 24, 25, 28, 29, 30, 31, 33, 37, 39, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.560515873015873</t>
+          <t>0.932967032967033</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.03687744091665674</t>
+          <t>0.04278905083452188</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.04153989204767869</t>
+          <t>0.0838475419395617</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.97444133501674</t>
+          <t>0.9038977704995418</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.2613236904144287</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.292802333831787</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 6, 8, 10, 11, 13, 19, 21, 22, 26, 31, 32, 35, 37, 42, 43, 44]</t>
+          <t>[1, 2, 8, 10, 12, 16, 17, 19, 22, 24, 27, 28, 29, 30, 31, 36, 37, 39, 42]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.7172619047619048</t>
+          <t>0.5675824175824176</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.03734124038301758</t>
+          <t>0.04535559322855694</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.037976010828875466</t>
+          <t>0.0567636774238504</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.9786387765330904</t>
+          <t>0.9559552814642025</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.3198461532592773</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.236677169799805</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[2, 4, 6, 8, 10, 13, 14, 18, 19, 21, 29, 32, 33, 34, 35, 37, 40, 43, 44]</t>
+          <t>[0, 2, 3, 4, 6, 8, 10, 12, 13, 15, 17, 20, 22, 23, 25, 26, 27, 29, 32, 34, 36, 37, 38, 44]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0.575595238095238</t>
+          <t>0.6186813186813187</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.04042533677010805</t>
+          <t>0.044795203868752034</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.052587881535965074</t>
+          <t>0.07427547109803564</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.959038222885853</t>
+          <t>0.9245874506878946</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.248765707015991</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.504666090011597</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[1, 2, 8, 11, 13, 14, 15, 16, 17, 19, 22, 23, 25, 26, 27, 28, 29, 30, 32, 36, 37, 38, 39, 40, 41, 42]</t>
+          <t>[4, 6, 8, 10, 13, 14, 19, 21, 23, 27, 29, 32, 35, 36, 37, 38, 44]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.2807539682539681</t>
+          <t>0.43736263736263736</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.043102685837030016</t>
+          <t>0.04596328481527069</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.050049401720014736</t>
+          <t>0.07648850058259918</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.9628973252703485</t>
+          <t>0.9200266870838247</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.2453079223632812</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.756611108779907</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 6, 8, 10, 12, 14, 21, 24, 26, 27, 29, 34, 37, 38, 39, 40, 41, 42, 43, 44]</t>
+          <t>[1, 2, 4, 5, 6, 7, 8, 10, 12, 13, 17, 19, 21, 23, 27, 29, 31, 36, 37, 39, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3173,375 +2848,330 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0.7871031746031746</t>
+          <t>0.6137362637362638</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.037729557482933454</t>
+          <t>0.048254464473119034</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.03873856981762998</t>
+          <t>0.0728453915355467</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.9777722960233148</t>
+          <t>0.9274634399158195</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2.335998058319092</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.629299879074097</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 5, 7, 8, 9, 10, 12, 13, 14, 15, 16, 17, 20, 26, 32, 34, 35, 37, 38, 40, 41, 42]</t>
+          <t>[1, 2, 3, 4, 6, 7, 11, 12, 13, 15, 21, 22, 23, 26, 28, 33, 35, 37, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.7914682539682539</t>
+          <t>0.506043956043956</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.0397742030716947</t>
+          <t>0.04661604436975888</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.03930949472240385</t>
+          <t>0.09596736093290453</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.9771122889891748</t>
+          <t>0.8741074888794778</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2.2880420684814453</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.547626495361328</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 8, 12, 18, 20, 21, 22, 23, 24, 25, 26, 31, 32, 33, 34, 37, 38, 43, 44]</t>
+          <t>[2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13, 15, 21, 22, 24, 25, 26, 27, 29, 32, 37, 38, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.4916666666666667</t>
+          <t>0.8692307692307693</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.040301786259381765</t>
+          <t>0.045297177196496764</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.03696514328059902</t>
+          <t>0.09747529554068521</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.9797608520075288</t>
+          <t>0.8701201095938713</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2.2029802799224854</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.038543939590454</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[3, 7, 8, 9, 10, 12, 13, 18, 20, 23, 28, 31, 35, 37, 43]</t>
+          <t>[0, 5, 7, 8, 10, 11, 12, 13, 14, 15, 16, 17, 19, 21, 22, 26, 28, 29, 30, 32, 37, 38, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.33075396825396824</t>
+          <t>0.9351648351648352</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.03599047396236953</t>
+          <t>0.04410298639696037</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.03737590305936141</t>
+          <t>0.0896180954008577</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.9793085546828135</t>
+          <t>0.8902146951896043</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2.1571450233459473</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.962615013122559</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 6, 7, 8, 9, 10, 11, 12, 14, 15, 16, 17, 18, 19, 20, 21, 26, 30, 35, 37, 39, 40, 43]</t>
+          <t>[1, 5, 7, 8, 11, 13, 14, 15, 17, 18, 21, 22, 23, 25, 27, 29, 32, 34, 37, 38, 39, 43]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0.7039682539682539</t>
+          <t>0.7972527472527473</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.04003959851477717</t>
+          <t>0.046533105811971766</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.048523504254604985</t>
+          <t>0.0881166608248177</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.9651251978578825</t>
+          <t>0.8938624998007478</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2.2425496578216553</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.544525384902954</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 8, 10, 11, 13, 15, 16, 17, 18, 23, 25, 28, 30, 32, 33, 35, 37, 38, 39]</t>
+          <t>[1, 4, 5, 6, 8, 11, 13, 14, 16, 17, 21, 24, 25, 29, 30, 34, 36, 37, 38, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.7700396825396825</t>
+          <t>0.8483516483516483</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.03826740393692505</t>
+          <t>0.046207317823759766</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.058141743211519</t>
+          <t>0.08609076976638919</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.9499293146830525</t>
+          <t>0.8986868136700414</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2.14884614944458</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.991122245788574</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 6, 8, 11, 12, 13, 16, 19, 24, 29, 37, 41, 43, 44]</t>
+          <t>[0, 1, 2, 4, 7, 8, 12, 14, 17, 21, 22, 26, 27, 30, 31, 33, 38, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.49682539682539684</t>
+          <t>0.37252747252747254</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.03853201930602183</t>
+          <t>0.042916339016973684</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.03750165997408787</t>
+          <t>0.08360756684083118</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.9791690814030363</t>
+          <t>0.9044470803321845</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2.223623514175415</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.695185661315918</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 8, 9, 11, 13, 14, 18, 23, 25, 26, 27, 30, 32, 35, 37, 38, 39]</t>
+          <t>[3, 6, 8, 10, 12, 13, 18, 22, 27, 29, 34, 37, 39, 40, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.7345238095238095</t>
+          <t>0.3631868131868132</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.038421232973739956</t>
+          <t>0.03787686580116155</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.048226582240217496</t>
+          <t>0.0769059249587098</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.965550699458816</t>
+          <t>0.9191514208463323</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2.275562286376953</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.04383111000061</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 5, 6, 7, 8, 12, 13, 14, 17, 18, 19, 20, 21, 22, 23, 24, 25, 27, 28, 31, 37, 40, 41]</t>
+          <t>[1, 3, 4, 6, 7, 8, 11, 13, 17, 19, 20, 21, 24, 27, 28, 34, 37, 38, 40]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.9742063492063493</t>
+          <t>0.65989010989011</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.039124839259410425</t>
+          <t>0.04418922871634498</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.02461293022467251</t>
+          <t>0.09758865279869448</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.9910270741415595</t>
+          <t>0.8698178506676849</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2.1610219478607178</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>7.062801361083984</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 5, 6, 7, 8, 11, 12, 14, 15, 16, 19, 23, 28, 29, 30, 31, 34, 37, 39, 44]</t>
+          <t>[3, 4, 5, 7, 8, 12, 13, 19, 21, 23, 24, 26, 27, 28, 32, 35, 37, 38, 39, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3551,81 +3181,71 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.6761904761904762</t>
+          <t>0.5038461538461538</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.03821781287304814</t>
+          <t>0.04326267415263605</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.028867968138513635</t>
+          <t>0.07720050810718765</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.9876564559044729</t>
+          <t>0.9185308641588004</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2.1602377891540527</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>7.048805475234985</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[3, 7, 8, 9, 11, 17, 19, 21, 24, 25, 30, 32, 37, 39, 40, 43]</t>
+          <t>[1, 4, 8, 9, 10, 12, 13, 14, 16, 18, 21, 22, 23, 24, 25, 26, 27, 28, 30, 31, 32, 34, 36, 37, 38, 44]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.531547619047619</t>
+          <t>0.6901098901098901</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.04190586741655184</t>
+          <t>0.042167841860778155</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.048236342829876495</t>
+          <t>0.06610588113436404</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.9655367536431515</t>
+          <t>0.9402644331792588</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2.220095157623291</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.595964431762695</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 8, 12, 13, 15, 17, 19, 22, 27, 28, 29, 34, 36, 37, 39, 41, 42, 43, 44]</t>
+          <t>[1, 3, 4, 5, 6, 10, 12, 14, 17, 18, 19, 20, 26, 27, 29, 30, 37, 39, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3635,165 +3255,145 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.0089285714285714</t>
+          <t>0.634065934065934</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.038390089041949474</t>
+          <t>0.047618828499768076</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.0470456263353842</t>
+          <t>0.07652615618816962</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.9672172072687243</t>
+          <t>0.919947925314998</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2.2124874591827393</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.157495975494385</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[1, 3, 6, 8, 9, 12, 14, 16, 18, 19, 24, 26, 27, 29, 34, 36, 37, 41, 44]</t>
+          <t>[2, 3, 4, 5, 7, 8, 10, 12, 14, 15, 16, 18, 21, 23, 25, 29, 30, 32, 34, 37, 39, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.5551587301587302</t>
+          <t>0.5159340659340659</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.037638862898626245</t>
+          <t>0.04232990522379385</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.05124545436432075</t>
+          <t>0.08659444716989928</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0.9611028183993122</t>
+          <t>0.8974978723509387</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2.314568281173706</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>7.140447378158569</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 5, 6, 8, 10, 11, 12, 14, 17, 20, 22, 25, 26, 27, 32, 37, 38, 43]</t>
+          <t>[3, 4, 6, 8, 13, 14, 15, 16, 17, 22, 23, 26, 27, 30, 32, 34, 36, 37, 38, 39, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.6529761904761905</t>
+          <t>0.6747252747252748</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.04097782454554469</t>
+          <t>0.04385218237002302</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.04478911642568716</t>
+          <t>0.08248662954489722</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.9702865946065021</t>
+          <t>0.9069920849182471</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2.2783007621765137</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.253865480422974</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 5, 6, 7, 8, 10, 11, 13, 17, 18, 19, 21, 23, 24, 26, 27, 30, 32, 33, 34, 37, 42]</t>
+          <t>[0, 3, 4, 5, 7, 8, 10, 11, 13, 16, 17, 18, 19, 20, 21, 22, 23, 24, 26, 27, 28, 32, 33, 37, 39, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.7186507936507937</t>
+          <t>1.0769230769230769</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.03947293780664292</t>
+          <t>0.0479881770540048</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.058447977235709235</t>
+          <t>0.08937767969562477</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.9494004785260062</t>
+          <t>0.8908029404101081</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2.2309272289276123</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>7.362762212753296</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 6, 7, 8, 13, 14, 17, 18, 19, 20, 21, 23, 24, 26, 27, 28, 34, 35, 37, 38, 41, 42, 43]</t>
+          <t>[3, 6, 8, 9, 10, 11, 12, 13, 19, 22, 23, 24, 25, 27, 29, 30, 31, 33, 35, 36, 37, 38, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3803,207 +3403,182 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.8878968253968254</t>
+          <t>0.8340659340659341</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.04003979975900875</t>
+          <t>0.047162111672981025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.04197782875717946</t>
+          <t>0.06877639908482852</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.9738995868839994</t>
+          <t>0.9353406015592837</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2.23637056350708</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.403211832046509</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 6, 8, 10, 12, 14, 16, 17, 20, 22, 23, 25, 28, 29, 35, 37, 39, 40, 41, 42, 43, 44]</t>
+          <t>[0, 1, 2, 4, 5, 6, 7, 8, 10, 12, 13, 14, 15, 18, 22, 23, 24, 28, 29, 33, 37, 38, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.8932539682539682</t>
+          <t>0.6824175824175824</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.040140572180604524</t>
+          <t>0.042092919382567665</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.04672088001186651</t>
+          <t>0.09403779173544055</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.9676682310235851</t>
+          <t>0.879119113435034</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2.2910172939300537</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.356555461883545</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 7, 9, 13, 14, 16, 17, 19, 20, 21, 24, 25, 35, 37, 38, 41, 44]</t>
+          <t>[2, 3, 4, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19, 20, 26, 29, 37, 39, 42]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.6595238095238095</t>
+          <t>0.48021978021978023</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.04156549768469832</t>
+          <t>0.04011832129314462</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.07111837075311611</t>
+          <t>0.09459216385772036</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.9250846115185742</t>
+          <t>0.8776896770334031</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2.2125353813171387</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>7.704412937164307</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 7, 12, 19, 20, 22, 26, 27, 29, 30, 31, 37, 38, 39, 40, 41]</t>
+          <t>[1, 2, 4, 6, 8, 10, 14, 15, 17, 20, 22, 24, 25, 28, 29, 35, 37, 38, 39, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.569047619047619</t>
+          <t>0.7434065934065934</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.03786546619901457</t>
+          <t>0.037710361076257505</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.027656766048931223</t>
+          <t>0.08322962900987158</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.9886705133972664</t>
+          <t>0.9053089985103815</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2.2565979957580566</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>7.505128860473633</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 6, 7, 10, 12, 13, 15, 18, 21, 25, 26, 28, 29, 32, 34, 37]</t>
+          <t>[3, 4, 8, 9, 10, 12, 15, 16, 17, 19, 20, 22, 23, 24, 26, 27, 28, 29, 31, 32, 33, 34, 37, 38, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.47718253968253965</t>
+          <t>0.615934065934066</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.03885478810752116</t>
+          <t>0.042325471935707695</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.05182668464205313</t>
+          <t>0.07314883614971915</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.9602154643064809</t>
+          <t>0.9268578649534427</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2.1923558712005615</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.27101993560791</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 7, 8, 9, 10, 12, 14, 17, 20, 22, 23, 24, 26, 28, 32, 36, 37, 38, 39, 40, 42]</t>
+          <t>[0, 2, 3, 6, 7, 8, 12, 13, 15, 19, 20, 21, 22, 24, 26, 29, 33, 37, 38, 39, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4013,249 +3588,219 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1.045436507936508</t>
+          <t>0.7285714285714285</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.04265970862713313</t>
+          <t>0.04385549277376648</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.05049351536617304</t>
+          <t>0.08586460265023899</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.9622359422555152</t>
+          <t>0.8992184296190187</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2.3189265727996826</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.06704568862915</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 7, 10, 13, 15, 16, 17, 20, 21, 22, 23, 24, 25, 26, 34, 35, 37, 40, 44]</t>
+          <t>[0, 1, 2, 5, 8, 10, 12, 13, 15, 24, 25, 29, 33, 35, 37, 38, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.36666666666666664</t>
+          <t>0.5159340659340659</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.038075116749856815</t>
+          <t>0.04704119860633309</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.04549913864751049</t>
+          <t>0.07838427166330716</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.9693370603459955</t>
+          <t>0.916013274957085</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2.194591760635376</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.178029775619507</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[1, 4, 5, 7, 10, 11, 15, 19, 22, 23, 25, 28, 31, 35, 37, 40, 42, 44]</t>
+          <t>[4, 5, 8, 9, 10, 11, 15, 16, 19, 20, 22, 24, 25, 27, 28, 31, 32, 35, 37, 39, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.691468253968254</t>
+          <t>1.0763736263736263</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.038308648629579126</t>
+          <t>0.045420975730006995</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.04536962705660269</t>
+          <t>0.06967579996465365</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.9695113737185035</t>
+          <t>0.9336384196975971</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2.2841899394989014</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>7.1691648960113525</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[3, 5, 8, 12, 13, 15, 16, 21, 24, 25, 27, 31, 37, 39, 41, 42, 43, 44]</t>
+          <t>[0, 3, 4, 6, 8, 10, 12, 14, 15, 16, 17, 19, 21, 22, 24, 25, 28, 32, 34, 36, 37, 38, 39, 40, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0.5251984126984127</t>
+          <t>1.1296703296703297</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.034972425089090514</t>
+          <t>0.04427656625770484</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.025611584176729225</t>
+          <t>0.07382498130845577</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.9902841607109939</t>
+          <t>0.9254994491993777</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2.2877650260925293</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.815295696258545</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 7, 8, 14, 17, 19, 26, 27, 31, 32, 33, 34, 35, 37, 38, 42]</t>
+          <t>[1, 2, 4, 6, 8, 12, 13, 14, 17, 18, 20, 21, 22, 26, 27, 29, 30, 31, 34, 37, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0.6755952380952381</t>
+          <t>0.5005494505494505</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.039377044563319905</t>
+          <t>0.04335038562259788</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.05075607242928368</t>
+          <t>0.07578276178335484</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.9618421887730038</t>
+          <t>0.9214956631995797</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2.2906785011291504</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.715996980667114</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[2, 3, 8, 9, 13, 14, 15, 17, 20, 23, 26, 31, 35, 36, 37, 40, 41, 42, 43, 44]</t>
+          <t>[4, 8, 9, 10, 11, 12, 13, 14, 16, 17, 18, 19, 20, 21, 22, 23, 25, 26, 28, 29, 30, 33, 34, 35, 37, 38, 39, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.6265873015873016</t>
+          <t>0.7917582417582417</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.04115727876013601</t>
+          <t>0.04110290369358673</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.045163935349875055</t>
+          <t>0.09099885528704608</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.9697871988473756</t>
+          <t>0.8868056758925343</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2.303234338760376</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.4676833152771</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[1, 2, 6, 8, 10, 11, 12, 14, 17, 27, 28, 30, 32, 37, 39, 40, 41, 42, 43]</t>
+          <t>[3, 4, 5, 8, 9, 10, 12, 13, 16, 17, 18, 19, 23, 31, 34, 37, 38, 39, 44]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4265,410 +3810,360 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0.8930555555555555</t>
+          <t>0.22472527472527473</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.03839338272717642</t>
+          <t>0.03960472672580569</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.04272702547264821</t>
+          <t>0.083950397384865</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.9729596220579657</t>
+          <t>0.9036618494432083</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2.2261977195739746</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.283301591873169</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 6, 7, 8, 14, 17, 24, 25, 31, 37, 39, 42, 44]</t>
+          <t>[3, 5, 8, 10, 12, 13, 19, 20, 21, 22, 23, 24, 25, 29, 30, 32, 35, 37, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0.3954365079365079</t>
+          <t>0.3192307692307692</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.036002347849372424</t>
+          <t>0.043358035233940266</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.03188776580165978</t>
+          <t>0.07315384931574652</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.9849389371214559</t>
+          <t>0.9268478391963519</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2.2241387367248535</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>6.14306902885437</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 8, 15, 17, 18, 24, 26, 27, 28, 35, 37, 39, 42, 43]</t>
+          <t>[1, 2, 3, 8, 12, 13, 16, 17, 18, 19, 20, 22, 23, 26, 27, 28, 29, 31, 35, 37, 39, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0.5867063492063492</t>
+          <t>0.6774725274725275</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.03494476019222913</t>
+          <t>0.04406878003648822</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.05653480823376083</t>
+          <t>0.0648404261807517</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.9526587975127427</t>
+          <t>0.9425295611255644</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2.247129440307617</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.090999603271484</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[3, 4, 9, 10, 12, 18, 20, 21, 27, 30, 35, 37, 39, 42, 44]</t>
+          <t>[2, 3, 4, 8, 9, 10, 13, 17, 20, 21, 23, 28, 29, 33, 37, 39, 40, 43]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0.19880952380952382</t>
+          <t>0.21208791208791208</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.03604964138345696</t>
+          <t>0.04676882571100982</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.060285057200834935</t>
+          <t>0.09578575255651452</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.9461697009029285</t>
+          <t>0.8745835153379523</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2.2190518379211426</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.172178506851196</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[3, 8, 9, 11, 12, 13, 14, 15, 17, 18, 20, 21, 23, 26, 28, 29, 30, 31, 32, 36, 37, 40, 42, 44]</t>
+          <t>[1, 2, 4, 8, 9, 12, 13, 14, 15, 16, 18, 19, 21, 22, 26, 27, 29, 30, 34, 37, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0.7611111111111111</t>
+          <t>0.40824175824175823</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.042418646463627065</t>
+          <t>0.04025366126672601</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0.04216785134341269</t>
+          <t>0.10072650523110106</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0.973662752645293</t>
+          <t>0.8613115404258033</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2.252683639526367</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.081538677215576</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 7, 15, 20, 23, 24, 25, 30, 35, 37, 39, 41, 42, 44]</t>
+          <t>[1, 2, 3, 8, 11, 12, 14, 15, 16, 17, 19, 25, 26, 27, 29, 30, 34, 37, 40, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.5005952380952381</t>
+          <t>0.6181318681318682</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.038838328091340954</t>
+          <t>0.044933089165073804</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.06597007635091917</t>
+          <t>0.11184464821620826</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.9355383509075342</t>
+          <t>0.8290050801433441</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2.140672445297241</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.354917764663696</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 5, 6, 8, 9, 11, 19, 25, 29, 32, 33, 35, 37, 41, 43]</t>
+          <t>[1, 2, 5, 7, 8, 9, 12, 16, 18, 21, 22, 24, 25, 29, 30, 32, 33, 34, 37, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.5757936507936507</t>
+          <t>0.3752747252747253</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.03421041514597741</t>
+          <t>0.04176447630722589</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.05269091112598172</t>
+          <t>0.09519393819429696</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.9588775619450829</t>
+          <t>0.8761285046466765</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2.197361707687378</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.1242992877960205</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 7, 10, 11, 12, 14, 23, 24, 29, 32, 35, 37, 39, 41, 42]</t>
+          <t>[2, 3, 4, 6, 8, 9, 10, 12, 13, 15, 16, 19, 20, 22, 25, 28, 29, 32, 35, 37, 38, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0.49444444444444446</t>
+          <t>0.9280219780219781</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.04046637009873809</t>
+          <t>0.04333976803389671</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.05599083677004985</t>
+          <t>0.07759664385091698</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.9535654379116315</t>
+          <t>0.91769264074187</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2.2291042804718018</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.3107123374938965</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 7, 9, 10, 11, 12, 14, 16, 18, 19, 21, 23, 33, 34, 35, 37]</t>
+          <t>[5, 6, 7, 8, 9, 10, 16, 18, 21, 22, 24, 25, 26, 28, 30, 31, 34, 36, 37, 39, 41, 42]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0.4736111111111111</t>
+          <t>0.8538461538461538</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.03879143655084071</t>
+          <t>0.04622155584259683</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.05810643702128091</t>
+          <t>0.05743118946522998</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.9499901064068478</t>
+          <t>0.9549133036326545</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2.185636281967163</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>6.171903133392334</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 8, 12, 13, 15, 16, 17, 22, 23, 25, 26, 27, 29, 32, 33, 34, 37, 38, 39, 40, 44]</t>
+          <t>[4, 5, 7, 8, 10, 12, 14, 15, 17, 23, 28, 29, 31, 32, 35, 37, 38, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0.5041666666666667</t>
+          <t>0.5697802197802198</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.04013177202559341</t>
+          <t>0.04193760408702529</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.04582958845103925</t>
+          <t>0.06792046133453637</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.9688900471530282</t>
+          <t>0.936939988380721</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2.206728219985962</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6.095717906951904</t>
         </is>
       </c>
     </row>
